--- a/Testing/Answer Keys/iMicroSeq_AnswerKey_S1_Municipal-Wastewater_v1.2.xlsx
+++ b/Testing/Answer Keys/iMicroSeq_AnswerKey_S1_Municipal-Wastewater_v1.2.xlsx
@@ -2526,17 +2526,17 @@
       </c>
       <c r="AL4" s="18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AM4" s="18" t="inlineStr">
         <is>
-          <t>Rainstorm [ENVO:01000879]</t>
+          <t>Wastewater screening process [GENEPIO:0101198]</t>
         </is>
       </c>
       <c r="AN4" s="18" t="inlineStr">
         <is>
-          <t>22 mm rainfall overnight on 2026-03-09; plant operating at elevated flow with partial bypass avoided.</t>
+          <t>Coarse bar screening upstream of the influent pump station; no chemical dosing in the 24 h prior to collection. Plant operating at elevated flow following 22 mm of rainfall overnight on 2026-03-09.</t>
         </is>
       </c>
       <c r="AO4" s="18" t="inlineStr">
@@ -6103,17 +6103,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Rainstorm [ENVO:01000879]</t>
+          <t>Wastewater screening process [GENEPIO:0101198]</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>22 mm rainfall overnight on 2026-03-09; plant operating at elevated flow with partial bypass avoided.</t>
+          <t>Coarse bar screening upstream of the influent pump station; no chemical dosing in the 24 h prior to collection. Plant operating at elevated flow following 22 mm of rainfall overnight on 2026-03-09.</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
